--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484737_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484737_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.720599999999999</v>
+        <v>8.654199999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>8.1175</v>
+        <v>7.7865</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6032</v>
+        <v>0.8677</v>
       </c>
       <c r="G2" t="n">
         <v>4.4069</v>
@@ -610,13 +610,13 @@
         <v>2.0757</v>
       </c>
       <c r="S2" t="n">
-        <v>1.9363</v>
+        <v>1.8699</v>
       </c>
       <c r="T2" t="n">
-        <v>1.7288</v>
+        <v>1.3978</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2076</v>
+        <v>0.4721</v>
       </c>
       <c r="V2" t="n">
         <v>1.2452</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. SIDDIQUE</t>
+          <t>M. MARZIALI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.6504</v>
+        <v>4.9102</v>
       </c>
       <c r="E3" t="n">
-        <v>4.3832</v>
+        <v>2.1339</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2672</v>
+        <v>2.7763</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.8331</v>
+        <v>4.3569</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.2207</v>
+        <v>3.1726</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.6124000000000001</v>
+        <v>1.1843</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0341</v>
+        <v>4.7061</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.0892</v>
+        <v>3.8253</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1234</v>
+        <v>0.8808</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.8673</v>
+        <v>-0.3492</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1315</v>
+        <v>-0.6526</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.7358</v>
+        <v>0.3035</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9435</v>
+        <v>-1.6983</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9435</v>
+        <v>-3.774</v>
       </c>
       <c r="R3" t="n">
-        <v>1.887</v>
+        <v>2.0757</v>
       </c>
       <c r="S3" t="n">
-        <v>3.2948</v>
+        <v>1.9498</v>
       </c>
       <c r="T3" t="n">
-        <v>2.8022</v>
+        <v>0.5982</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4927</v>
+        <v>1.3516</v>
       </c>
       <c r="V3" t="n">
-        <v>1.2452</v>
+        <v>0.3018</v>
       </c>
       <c r="W3" t="n">
-        <v>2.4904</v>
+        <v>0.6036</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.2452</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. MARZIALI</t>
+          <t>A. KLEINJAN RODRIGUEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.5888</v>
+        <v>3.9381</v>
       </c>
       <c r="E4" t="n">
-        <v>1.257</v>
+        <v>2.9507</v>
       </c>
       <c r="F4" t="n">
-        <v>3.3318</v>
+        <v>0.9875</v>
       </c>
       <c r="G4" t="n">
-        <v>4.3569</v>
+        <v>3.9955</v>
       </c>
       <c r="H4" t="n">
-        <v>3.1726</v>
+        <v>1.8939</v>
       </c>
       <c r="I4" t="n">
-        <v>1.1843</v>
+        <v>2.1016</v>
       </c>
       <c r="J4" t="n">
-        <v>4.7061</v>
+        <v>5.2541</v>
       </c>
       <c r="K4" t="n">
-        <v>3.8253</v>
+        <v>3.1961</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8808</v>
+        <v>2.058</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.3492</v>
+        <v>-1.2586</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6526</v>
+        <v>-1.3022</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3035</v>
+        <v>0.0437</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.6983</v>
+        <v>-0.5661</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.774</v>
+        <v>-2.8305</v>
       </c>
       <c r="R4" t="n">
-        <v>2.0757</v>
+        <v>2.2644</v>
       </c>
       <c r="S4" t="n">
-        <v>1.6284</v>
+        <v>0.8105</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2787</v>
+        <v>0.5271</v>
       </c>
       <c r="U4" t="n">
-        <v>1.9071</v>
+        <v>0.2834</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3018</v>
+        <v>-0.3018</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6036</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>-0.3018</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. KLEINJAN RODRIGUEZ</t>
+          <t>S. SIDDIQUE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.9994</v>
+        <v>3.6987</v>
       </c>
       <c r="E5" t="n">
-        <v>2.8532</v>
+        <v>3.2728</v>
       </c>
       <c r="F5" t="n">
-        <v>1.1462</v>
+        <v>0.4259</v>
       </c>
       <c r="G5" t="n">
-        <v>3.9955</v>
+        <v>-0.8331</v>
       </c>
       <c r="H5" t="n">
-        <v>1.8939</v>
+        <v>-0.2207</v>
       </c>
       <c r="I5" t="n">
-        <v>2.1016</v>
+        <v>-0.6124000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>5.2541</v>
+        <v>0.0341</v>
       </c>
       <c r="K5" t="n">
-        <v>3.1961</v>
+        <v>-0.0892</v>
       </c>
       <c r="L5" t="n">
-        <v>2.058</v>
+        <v>0.1234</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.2586</v>
+        <v>-0.8673</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.3022</v>
+        <v>-0.1315</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0437</v>
+        <v>-0.7358</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.5661</v>
+        <v>0.9435</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.8305</v>
+        <v>-0.9435</v>
       </c>
       <c r="R5" t="n">
-        <v>2.2644</v>
+        <v>1.887</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8718</v>
+        <v>2.3431</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4296</v>
+        <v>1.6918</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4421</v>
+        <v>0.6514</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.3018</v>
+        <v>1.2452</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.4904</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.3018</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.698</v>
+        <v>0.8613</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4632</v>
+        <v>-0.6967</v>
       </c>
       <c r="F6" t="n">
-        <v>1.1612</v>
+        <v>1.558</v>
       </c>
       <c r="G6" t="n">
         <v>-1.0202</v>
@@ -922,13 +922,13 @@
         <v>1.6983</v>
       </c>
       <c r="S6" t="n">
-        <v>1.907</v>
+        <v>2.0703</v>
       </c>
       <c r="T6" t="n">
-        <v>1.8463</v>
+        <v>1.6128</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0606</v>
+        <v>0.4574</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. ORTOLA TOMAS</t>
+          <t>U. ZAMORA MAÑA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6258</v>
+        <v>0.617</v>
       </c>
       <c r="E7" t="n">
-        <v>1.1072</v>
+        <v>0.617</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4814</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.7117</v>
+        <v>0.617</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.378</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.3337</v>
+        <v>0.617</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.2709</v>
+        <v>0.617</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3702</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.641</v>
+        <v>0.617</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.4408</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7482</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6927</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7548</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7548</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.2809</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1.0763</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2046</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3018</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.3018</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>U. ZAMORA MAÑA</t>
+          <t>J. ORTOLA TOMAS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.617</v>
+        <v>0.0122</v>
       </c>
       <c r="E8" t="n">
-        <v>0.617</v>
+        <v>0.6788</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>-0.6666</v>
       </c>
       <c r="G8" t="n">
-        <v>0.617</v>
+        <v>-1.7117</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>-0.378</v>
       </c>
       <c r="I8" t="n">
-        <v>0.617</v>
+        <v>-1.3337</v>
       </c>
       <c r="J8" t="n">
-        <v>0.617</v>
+        <v>-0.2709</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>0.3702</v>
       </c>
       <c r="L8" t="n">
-        <v>0.617</v>
+        <v>-0.641</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>-1.4408</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>-0.7482</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>-0.6927</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.7548</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>0.7548</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>0.6673</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>0.6479</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>0.0194</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.3018</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.3018</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.1041</v>
+        <v>-1.8912</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.3665</v>
+        <v>-3.0742</v>
       </c>
       <c r="F9" t="n">
-        <v>1.2623</v>
+        <v>1.183</v>
       </c>
       <c r="G9" t="n">
         <v>-4.2762</v>
@@ -1156,13 +1156,13 @@
         <v>1.3209</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2287</v>
+        <v>0.4416</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1735</v>
+        <v>0.1188</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4022</v>
+        <v>0.3228</v>
       </c>
       <c r="V9" t="n">
         <v>1.566</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.4159</v>
+        <v>-2.292</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.3621</v>
+        <v>-1.2647</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.0538</v>
+        <v>-1.0273</v>
       </c>
       <c r="G10" t="n">
         <v>-1.9722</v>
@@ -1234,13 +1234,13 @@
         <v>0.3774</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2175</v>
+        <v>-0.0936</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1052</v>
+        <v>-0.0078</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1123</v>
+        <v>-0.0858</v>
       </c>
       <c r="V10" t="n">
         <v>-0.6036</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.5062</v>
+        <v>-2.3408</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.3072</v>
+        <v>-2.2741</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.199</v>
+        <v>-0.0667</v>
       </c>
       <c r="G11" t="n">
         <v>-3.1828</v>
@@ -1312,13 +1312,13 @@
         <v>1.6983</v>
       </c>
       <c r="S11" t="n">
-        <v>0.8089</v>
+        <v>1.9743</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2039</v>
+        <v>1.2371</v>
       </c>
       <c r="U11" t="n">
-        <v>0.6049</v>
+        <v>0.7372</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>15.8738</v>
+        <v>16.1677</v>
       </c>
       <c r="E12" t="n">
-        <v>9.836100000000002</v>
+        <v>10.13</v>
       </c>
       <c r="F12" t="n">
-        <v>6.0377</v>
+        <v>6.0378</v>
       </c>
       <c r="G12" t="n">
         <v>0.3801000000000001</v>
@@ -1381,7 +1381,7 @@
         <v>-4.0024</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.220446049250313e-16</v>
       </c>
       <c r="Q12" t="n">
         <v>-14.1525</v>
@@ -1390,13 +1390,13 @@
         <v>14.1525</v>
       </c>
       <c r="S12" t="n">
-        <v>11.7393</v>
+        <v>12.0332</v>
       </c>
       <c r="T12" t="n">
-        <v>7.5297</v>
+        <v>7.823700000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>4.2095</v>
+        <v>4.209499999999999</v>
       </c>
       <c r="V12" t="n">
         <v>3.7546</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.2429</v>
+        <v>3.5593</v>
       </c>
       <c r="E13" t="n">
-        <v>3.5271</v>
+        <v>3.8194</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.2842</v>
+        <v>-0.2601</v>
       </c>
       <c r="G13" t="n">
         <v>3.8823</v>
@@ -1468,13 +1468,13 @@
         <v>1.5096</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.2056</v>
+        <v>-0.8892</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5168</v>
+        <v>-0.2244</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6889</v>
+        <v>-0.6647999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>-0.9434</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.1461</v>
+        <v>2.0884</v>
       </c>
       <c r="E14" t="n">
         <v>1.3045</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8416</v>
+        <v>0.784</v>
       </c>
       <c r="G14" t="n">
         <v>2.4317</v>
@@ -1546,13 +1546,13 @@
         <v>2.4531</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.6066</v>
+        <v>-1.6642</v>
       </c>
       <c r="T14" t="n">
         <v>-0.6191</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.9875</v>
+        <v>-1.0451</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.366</v>
+        <v>-0.8116</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.2562</v>
+        <v>-1.9639</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8902</v>
+        <v>1.1524</v>
       </c>
       <c r="G15" t="n">
         <v>1.3886</v>
@@ -1624,13 +1624,13 @@
         <v>1.3209</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.2451</v>
+        <v>-0.6906</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5879</v>
+        <v>-0.2956</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6572</v>
+        <v>-0.395</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.4033</v>
+        <v>-1.2529</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.4192</v>
+        <v>-0.3218</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.984</v>
+        <v>-0.9311</v>
       </c>
       <c r="G16" t="n">
         <v>-1.0735</v>
@@ -1702,13 +1702,13 @@
         <v>0.3774</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5185</v>
+        <v>-0.3681</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2939</v>
+        <v>-0.1965</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2246</v>
+        <v>-0.1716</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. LOPEZ-VALVERDE CARRASCO</t>
+          <t>S. GALVEZ ARROYO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.5452</v>
+        <v>-2.0494</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.6006</v>
+        <v>-0.2344</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.9446</v>
+        <v>-1.8151</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.5916</v>
+        <v>0.9273</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.2367</v>
+        <v>-0.6918</v>
       </c>
       <c r="I17" t="n">
-        <v>0.645</v>
+        <v>1.6191</v>
       </c>
       <c r="J17" t="n">
-        <v>1.0426</v>
+        <v>2.2947</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.3162</v>
+        <v>0.9359</v>
       </c>
       <c r="L17" t="n">
         <v>1.3588</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.6342</v>
+        <v>-1.3674</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.9205</v>
+        <v>-1.6278</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.7137</v>
+        <v>0.2604</v>
       </c>
       <c r="P17" t="n">
-        <v>1.3209</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.3209</v>
+        <v>-2.2644</v>
       </c>
       <c r="R17" t="n">
-        <v>2.6418</v>
+        <v>2.2644</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.2744</v>
+        <v>-1.7315</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3223</v>
+        <v>-0.5665</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.9522</v>
+        <v>-1.165</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-1.2452</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.3018</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.547</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. GALVEZ ARROYO</t>
+          <t>P. LOPEZ-VALVERDE CARRASCO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.1319</v>
+        <v>-2.167</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.819</v>
+        <v>-1.0878</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.313</v>
+        <v>-1.0792</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9273</v>
+        <v>-1.5916</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6918</v>
+        <v>-2.2367</v>
       </c>
       <c r="I18" t="n">
-        <v>1.6191</v>
+        <v>0.645</v>
       </c>
       <c r="J18" t="n">
-        <v>2.2947</v>
+        <v>1.0426</v>
       </c>
       <c r="K18" t="n">
-        <v>0.9359</v>
+        <v>-0.3162</v>
       </c>
       <c r="L18" t="n">
         <v>1.3588</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.3674</v>
+        <v>-2.6342</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.6278</v>
+        <v>-1.9205</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2604</v>
+        <v>-0.7137</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.3209</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.2644</v>
+        <v>-1.3209</v>
       </c>
       <c r="R18" t="n">
-        <v>2.2644</v>
+        <v>2.6418</v>
       </c>
       <c r="S18" t="n">
-        <v>-2.814</v>
+        <v>-1.8963</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.1511</v>
+        <v>-0.8094</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.6629</v>
+        <v>-1.0868</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.2452</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.3018</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.547</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-5.4107</v>
+        <v>-5.7777</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.4368</v>
+        <v>-3.1188</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.974</v>
+        <v>-2.6589</v>
       </c>
       <c r="G19" t="n">
         <v>-3.8411</v>
@@ -1936,13 +1936,13 @@
         <v>1.5096</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.1358</v>
+        <v>-1.5027</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1357</v>
+        <v>-0.5463</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.2715</v>
+        <v>-0.9564</v>
       </c>
       <c r="V19" t="n">
         <v>-0.6226</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-8.4056</v>
+        <v>-8.1639</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.3374</v>
+        <v>-4.4348</v>
       </c>
       <c r="F20" t="n">
-        <v>-4.0682</v>
+        <v>-3.729</v>
       </c>
       <c r="G20" t="n">
         <v>-2.5037</v>
@@ -2014,13 +2014,13 @@
         <v>2.0757</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.9393</v>
+        <v>-1.6976</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8542</v>
+        <v>-0.9517</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.0851</v>
+        <v>-0.7459</v>
       </c>
       <c r="V20" t="n">
         <v>-0.9434</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-15.8737</v>
+        <v>-14.5748</v>
       </c>
       <c r="E21" t="n">
         <v>-6.037599999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>-9.836200000000002</v>
+        <v>-8.536999999999999</v>
       </c>
       <c r="G21" t="n">
         <v>-0.379999999999999</v>
@@ -2092,13 +2092,13 @@
         <v>14.1525</v>
       </c>
       <c r="S21" t="n">
-        <v>-11.7393</v>
+        <v>-10.4402</v>
       </c>
       <c r="T21" t="n">
-        <v>-4.2096</v>
+        <v>-4.2095</v>
       </c>
       <c r="U21" t="n">
-        <v>-7.5299</v>
+        <v>-6.2306</v>
       </c>
       <c r="V21" t="n">
         <v>-3.7546</v>
